--- a/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rivenditore autorizzato Karcher/Nilfisk Alto/Roto per la contea di Bjelovar-Bilogora, con usisavaci industriali incl. linea EX/ATEX per zona 22. Sede: Naselje kralja Zvonimira 5/1 e negozio Ulica Vlahe Paljetka 5A, Bjelovar.</t>
+          <t>Rivenditore autorizzato Karcher/Nilfisk Alto/Roto per la contea di Bjelovar-Bilogora, con usisavaci industriali incl. linea EX/ATEX per zona 22. Sede: Naselje kralja Zvonimira 5/1 e negozio Ulica Vlahe Paljetka 5A, Bjelovar. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/servicer ufficiale Nilfisk (dal 2013), macchine per pulizia professionale gamma industriale.</t>
+          <t>Distributore/servicer ufficiale Nilfisk (dal 2013), macchine per pulizia professionale gamma industriale. [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -600,7 +600,6 @@
           <t>Ex-Oprema d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Virovitičko-podravska (copertura regionale/nazionale, sede a Zagreb)</t>
@@ -616,10 +615,9 @@
           <t>+385 1 5616 110</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Protezione antiesplosione e commercio all'ingrosso apparecchiature elettriche Ex (rappresentante Stahl). Sede Rapska 26/1, Zagreb; esistenza confermata da directory aziendale, nessun sito proprio verificabile.</t>
+          <t>Protezione antiesplosione e commercio all'ingrosso apparecchiature elettriche Ex (rappresentante Stahl). Sede Rapska 26/1, Zagreb; esistenza confermata da directory aziendale, nessun sito proprio verificabile. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -780,7 +778,6 @@
           <t>0913461101</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Produttore/distributore usisavaci industriali (monofase, trifase, aria compressa) incl. versione ATEX. Indirizzo: V. Skorpika 14b, 10090 Zagreb.</t>
@@ -818,10 +815,9 @@
           <t>+385 1 3707 288</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Filiale ufficiale gruppo SMC, componentistica pneumatica/automazione (catalogo SMC globale include gamma certificata ATEX). Sede: Zagrebacka avenija 106, Zagreb.</t>
+          <t>Filiale ufficiale gruppo SMC, componentistica pneumatica/automazione (catalogo SMC globale include gamma certificata ATEX). Sede: Zagrebacka avenija 106, Zagreb. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -851,8 +847,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Azienda slovena con espansione confermata anche in Croazia, BiH, Serbia, Macedonia del Nord; automazione industriale e componentistica Ex/ATEX. Nessun indirizzo/contatto specifico per l'entita croata reperibile.</t>

--- a/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Produttore sistemi di filtrazione/ventilazione industriale, incl. linea 'Ex izvedba' conforme Direttiva ATEX 2014/34/EU. Indirizzo: Zagorska ulica 24, 10297 Jakovlje.</t>
+          <t>Produttore sistemi di filtrazione/ventilazione industriale, incl. linea 'Ex izvedba' conforme Direttiva ATEX 2014/34/EU. Indirizzo: Zagorska ulica 24, 10297 Jakovlje. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Produttore leader regionale di apparecchiature elettriche antideflagranti Ex (illuminazione, quadri, prese). Sede legale Medarska 69, Zagreb; stabilimento produttivo a Zabok.</t>
+          <t>Produttore leader regionale di apparecchiature elettriche antideflagranti Ex (illuminazione, quadri, prese). Sede legale Medarska 69, Zagreb; stabilimento produttivo a Zabok. [DUPLICATO — vedi anche: 2026-09-08_03_Croazia_Krapinsko-zagorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">

--- a/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-15_00_Croazia_Virovitico-podravska_ATEX_Equipment-Services.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Produttore/distributore usisavaci industriali (monofase, trifase, aria compressa) incl. versione ATEX. Indirizzo: V. Skorpika 14b, 10090 Zagreb.</t>
+          <t>Produttore/distributore usisavaci industriali (monofase, trifase, aria compressa) incl. versione ATEX. Indirizzo: V. Skorpika 14b, 10090 Zagreb. [DUPLICATO — vedi anche: 2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Azienda slovena con espansione confermata anche in Croazia, BiH, Serbia, Macedonia del Nord; automazione industriale e componentistica Ex/ATEX. Nessun indirizzo/contatto specifico per l'entita croata reperibile.</t>
+          <t>Azienda slovena con espansione confermata anche in Croazia, BiH, Serbia, Macedonia del Nord; automazione industriale e componentistica Ex/ATEX. Nessun indirizzo/contatto specifico per l'entita croata reperibile. [DUPLICATO — vedi anche: 2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
